--- a/output/2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx
@@ -494,7 +494,6 @@
           <t>085 9159711</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Filiale della catena nazionale Sonepar Italia S.p.A. (distributore generalista di materiale elettrico industriale). Indirizzo confermato: Via Raiale, 305, 65128 Pescara. Presenza di linea prodotti ATEX/antideflagrante confermata dal catalogo online Sonepar (contenitori, interruttori, prese CEE antideflagranti a marchio CORTEM, PALAZZOLI, SCAME PARRE, classi 1G/2G/3G-1D/2D/3D). Non e' uno specialista ATEX dedicato.</t>
@@ -532,10 +531,9 @@
           <t>085 4463759</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Filiale ex Dime S.r.l. (azienda abruzzese acquisita da Sonepar Italia, accordo effettivo dal 1/1/2023, sede storica a San Giovanni Teatino CH) confermata da articoli di settore (impiantinews.it, automazionenews.it, abruzzoweb.it). Telefono ripreso da fonte grezza, non riconfermato in modo indipendente. Linea ATEX confermata a livello di catalogo nazionale Sonepar.</t>
+          <t>Filiale ex Dime S.r.l. (azienda abruzzese acquisita da Sonepar Italia, accordo effettivo dal 1/1/2023, sede storica a San Giovanni Teatino CH) confermata da articoli di settore (impiantinews.it, automazionenews.it, abruzzoweb.it). Telefono ripreso da fonte grezza, non riconfermato in modo indipendente. Linea ATEX confermata a livello di catalogo nazionale Sonepar. [DUPLICATO — vedi anche: 2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -570,10 +568,9 @@
           <t>0862 700611</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Filiale ex Dime (L'Aquila citata tra le sedi acquisite). Indirizzo e telefono confermati tramite pagina store-locator Sonepar (Via dell'Industria, snc, 67100 Bazzano-L'Aquila). Linea ATEX confermata a livello di catalogo nazionale Sonepar.</t>
+          <t>Filiale ex Dime (L'Aquila citata tra le sedi acquisite). Indirizzo e telefono confermati tramite pagina store-locator Sonepar (Via dell'Industria, snc, 67100 Bazzano-L'Aquila). Linea ATEX confermata a livello di catalogo nazionale Sonepar. [DUPLICATO — vedi anche: 2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -608,10 +605,9 @@
           <t>0861 777081</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Filiale ex Dime (Tortoreto Lido TE citata tra le sedi acquisite negli articoli di settore). Telefono ripreso da fonte grezza, non riconfermato in modo indipendente. Linea ATEX confermata a livello di catalogo nazionale Sonepar.</t>
+          <t>Filiale ex Dime (Tortoreto Lido TE citata tra le sedi acquisite negli articoli di settore). Telefono ripreso da fonte grezza, non riconfermato in modo indipendente. Linea ATEX confermata a livello di catalogo nazionale Sonepar. [DUPLICATO — vedi anche: 2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -646,10 +642,9 @@
           <t>0861 413086</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Filiale confermata: Viale Europa - S.S. 80 bivio Nepezzano, 64100 Teramo. Telefono reperito da ricerca web (non da fetch diretto pagina store), da confermare. Linea ATEX confermata a livello di catalogo nazionale Sonepar.</t>
+          <t>Filiale confermata: Viale Europa - S.S. 80 bivio Nepezzano, 64100 Teramo. Telefono reperito da ricerca web (non da fetch diretto pagina store), da confermare. Linea ATEX confermata a livello di catalogo nazionale Sonepar. [DUPLICATO — vedi anche: 2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -679,7 +674,6 @@
           <t>ATEX Equipment/Services</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>info@safexpert.it</t>

--- a/output/2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-02_06_Italia_Abruzzo_ATEX_Equipment-Services.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/09/2026)</t>
         </is>
       </c>
     </row>
